--- a/stick-world/config/excel/资源数据.xlsx
+++ b/stick-world/config/excel/资源数据.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="resources" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="资源" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/stick-world/config/excel/资源数据.xlsx
+++ b/stick-world/config/excel/资源数据.xlsx
@@ -2,15 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="25000" windowHeight="10000" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="资源" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="171027" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -35,7 +34,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -47,6 +46,9 @@
         <fgColor rgb="00D9D9D9"/>
         <bgColor rgb="00D9D9D9"/>
       </patternFill>
+    </fill>
+    <fill>
+      <patternFill/>
     </fill>
   </fills>
   <borders count="2">
@@ -62,24 +64,25 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -440,8 +443,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:G8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelRow="0"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
@@ -453,291 +456,260 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>name_zh</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>category</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>base_price</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>weight_per_unit</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>perishable</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>icon_path</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B2" s="1" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>名称</t>
         </is>
       </c>
-      <c r="C2" s="1" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>类别</t>
         </is>
       </c>
-      <c r="D2" s="1" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>基础价格</t>
         </is>
       </c>
-      <c r="E2" s="1" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>单位重量</t>
         </is>
       </c>
-      <c r="F2" s="1" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>是否易腐</t>
         </is>
       </c>
-      <c r="G2" s="1" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>图标路径</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>res_food</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>食物</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>res_wood</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>木材</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
         <is>
           <t>basic</t>
         </is>
       </c>
-      <c r="D3" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F3" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>res://assets/icons/food.png</t>
+      <c r="D3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>res://assets/icons/wood.png</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>res_wood</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>木材</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>res_stone</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>石料</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
         <is>
           <t>basic</t>
         </is>
       </c>
-      <c r="D4" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="F4" s="2" t="b">
+      <c r="D4" t="n">
+        <v>4</v>
+      </c>
+      <c r="E4" t="n">
+        <v>5</v>
+      </c>
+      <c r="F4" t="b">
         <v>0</v>
       </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>res://assets/icons/wood.png</t>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>res://assets/icons/stone.png</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>res_stone</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>石料</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>res_metal_ore</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>金属矿</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
         <is>
           <t>basic</t>
         </is>
       </c>
-      <c r="D5" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="F5" s="2" t="b">
+      <c r="D5" t="n">
+        <v>8</v>
+      </c>
+      <c r="E5" t="n">
+        <v>8</v>
+      </c>
+      <c r="F5" t="b">
         <v>0</v>
       </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>res://assets/icons/stone.png</t>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>res://assets/icons/metal_ore.png</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>res_metal_ore</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>金属矿</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>basic</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="E6" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="F6" s="2" t="b">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>res_black_asphalt</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>黑色沥青</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>strategic</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>15</v>
+      </c>
+      <c r="E6" t="n">
+        <v>6</v>
+      </c>
+      <c r="F6" t="b">
         <v>0</v>
       </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>res://assets/icons/metal_ore.png</t>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>res://assets/icons/black_asphalt.png</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>res_black_asphalt</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>黑色沥青</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>strategic</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="E7" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="F7" s="2" t="b">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>res_iron_ingot</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>铁锭</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>processed</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>20</v>
+      </c>
+      <c r="E7" t="n">
+        <v>7</v>
+      </c>
+      <c r="F7" t="b">
         <v>0</v>
       </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>res://assets/icons/black_asphalt.png</t>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>res://assets/icons/iron_ingot.png</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>res_iron_ingot</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>铁锭</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>processed</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="E8" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="F8" s="2" t="b">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>res_silk</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>布料</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>luxury</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>50</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F8" t="b">
         <v>0</v>
       </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>res://assets/icons/iron_ingot.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>res_silk</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>丝绸</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>luxury</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F9" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>res://assets/icons/silk.png</t>
         </is>

--- a/stick-world/config/excel/资源数据.xlsx
+++ b/stick-world/config/excel/资源数据.xlsx
@@ -6,7 +6,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="25000" windowHeight="10000" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="资源" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="resources" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="171027" fullCalcOnLoad="1"/>
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelRow="0"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -458,117 +458,93 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>name_zh</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>category</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>base_price</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>weight_per_unit</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>perishable</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>icon_path</t>
+          <t>#output_dir: resources</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>id</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>名称</t>
+          <t>name_zh</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>类别</t>
+          <t>category</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>基础价格</t>
+          <t>base_price</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>单位重量</t>
+          <t>weight_per_unit</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>是否易腐</t>
+          <t>perishable</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>图标路径</t>
+          <t>icon_path</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>res_wood</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>木材</t>
+          <t>名称</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>basic</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>3</v>
-      </c>
-      <c r="E3" t="n">
-        <v>2</v>
-      </c>
-      <c r="F3" t="b">
-        <v>0</v>
+          <t>类别</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>基础价格</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>单位重量</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>是否易腐</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>res://assets/icons/wood.png</t>
+          <t>图标路径</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>res_stone</t>
+          <t>res_wood</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>石料</t>
+          <t>木材</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -577,29 +553,29 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F4" t="b">
         <v>0</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>res://assets/icons/stone.png</t>
+          <t>res://assets/icons/wood.png</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>res_metal_ore</t>
+          <t>res_stone</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>金属矿</t>
+          <t>石料</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -608,108 +584,139 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E5" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F5" t="b">
         <v>0</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>res://assets/icons/metal_ore.png</t>
+          <t>res://assets/icons/stone.png</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>res_black_asphalt</t>
+          <t>res_metal_ore</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>黑色沥青</t>
+          <t>金属矿</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>strategic</t>
+          <t>basic</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E6" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F6" t="b">
         <v>0</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>res://assets/icons/black_asphalt.png</t>
+          <t>res://assets/icons/metal_ore.png</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>res_iron_ingot</t>
+          <t>res_black_asphalt</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>铁锭</t>
+          <t>黑色沥青</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>processed</t>
+          <t>strategic</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F7" t="b">
         <v>0</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>res://assets/icons/iron_ingot.png</t>
+          <t>res://assets/icons/black_asphalt.png</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>res_silk</t>
+          <t>res_iron_ingot</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>布料</t>
+          <t>铁锭</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>luxury</t>
+          <t>processed</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="E8" t="n">
-        <v>0.5</v>
+        <v>7</v>
       </c>
       <c r="F8" t="b">
         <v>0</v>
       </c>
       <c r="G8" t="inlineStr">
+        <is>
+          <t>res://assets/icons/iron_ingot.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>res_silk</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>布料</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>luxury</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>50</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F9" t="b">
+        <v>0</v>
+      </c>
+      <c r="G9" t="inlineStr">
         <is>
           <t>res://assets/icons/silk.png</t>
         </is>

--- a/stick-world/config/excel/资源数据.xlsx
+++ b/stick-world/config/excel/资源数据.xlsx
@@ -480,7 +480,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>base_price</t>
+          <t>initial_price</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -517,7 +517,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>基础价格</t>
+          <t>initial_price</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -555,8 +555,10 @@
       <c r="D4" t="n">
         <v>3</v>
       </c>
-      <c r="E4" t="n">
-        <v>2</v>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="F4" t="b">
         <v>0</v>
@@ -586,8 +588,10 @@
       <c r="D5" t="n">
         <v>4</v>
       </c>
-      <c r="E5" t="n">
-        <v>5</v>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="F5" t="b">
         <v>0</v>
@@ -617,8 +621,10 @@
       <c r="D6" t="n">
         <v>8</v>
       </c>
-      <c r="E6" t="n">
-        <v>8</v>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="F6" t="b">
         <v>0</v>
@@ -648,8 +654,10 @@
       <c r="D7" t="n">
         <v>15</v>
       </c>
-      <c r="E7" t="n">
-        <v>6</v>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="F7" t="b">
         <v>0</v>
@@ -679,8 +687,10 @@
       <c r="D8" t="n">
         <v>20</v>
       </c>
-      <c r="E8" t="n">
-        <v>7</v>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
       <c r="F8" t="b">
         <v>0</v>
@@ -699,7 +709,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>布料</t>
+          <t>丝绸</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -710,8 +720,10 @@
       <c r="D9" t="n">
         <v>50</v>
       </c>
-      <c r="E9" t="n">
-        <v>0.5</v>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
       </c>
       <c r="F9" t="b">
         <v>0</v>
